--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776C48EF-0509-4E96-88C6-2D59A7FF847D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC46080-9CAB-4E93-A87F-CAF609E22C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80580" yWindow="990" windowWidth="30105" windowHeight="18735" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
+    <workbookView xWindow="57405" yWindow="1815" windowWidth="26355" windowHeight="18555" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="140">
   <si>
     <t>губ</t>
   </si>
@@ -454,6 +454,9 @@
   </si>
   <si>
     <t>Астраханская (кочевники)</t>
+  </si>
+  <si>
+    <t>Таблица из ежегодника УГВИ стр. 3-5</t>
   </si>
 </sst>
 </file>
@@ -472,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,6 +485,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -517,6 +526,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,9 +861,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB8BCAD-C8EF-4299-8ADC-574309E923F5}">
-  <dimension ref="A3:E32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>116</v>
@@ -2684,8 +2699,8 @@
       <c r="B48" s="1">
         <v>1522537</v>
       </c>
-      <c r="C48" s="1">
-        <v>78861</v>
+      <c r="C48" s="8">
+        <v>78061</v>
       </c>
       <c r="D48" s="1">
         <v>55549</v>
@@ -2698,7 +2713,7 @@
       </c>
       <c r="K48" s="2">
         <f t="shared" si="0"/>
-        <v>51.795785586819896</v>
+        <v>51.270346796169811</v>
       </c>
       <c r="L48" s="2">
         <f t="shared" si="1"/>
@@ -2706,7 +2721,7 @@
       </c>
       <c r="Q48" s="2">
         <f t="shared" si="2"/>
-        <v>-9.5785586819893354E-2</v>
+        <v>0.4296532038301919</v>
       </c>
       <c r="R48" s="2">
         <f t="shared" si="3"/>
@@ -3494,7 +3509,7 @@
       </c>
       <c r="I70" s="1">
         <f>SUM(C32:C69)</f>
-        <v>3034463</v>
+        <v>3033663</v>
       </c>
       <c r="J70" s="1">
         <f>SUM(D32:D69)</f>
@@ -3514,7 +3529,7 @@
       </c>
       <c r="O70" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="P70" s="1">
         <f t="shared" si="8"/>
@@ -3613,7 +3628,7 @@
       </c>
       <c r="I72" s="1">
         <f t="shared" ref="I72:J72" si="9">SUM(I16:I71)</f>
-        <v>4370998</v>
+        <v>4370198</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" si="9"/>
@@ -3633,7 +3648,7 @@
       </c>
       <c r="O72" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="P72" s="1">
         <f t="shared" si="8"/>
@@ -4750,7 +4765,7 @@
       </c>
       <c r="I104" s="1">
         <f t="shared" ref="I104:J104" si="14">SUM(I72:I103)</f>
-        <v>4884446</v>
+        <v>4883646</v>
       </c>
       <c r="J104" s="1">
         <f t="shared" si="14"/>
@@ -4770,7 +4785,7 @@
       </c>
       <c r="O104" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="P104" s="1">
         <f t="shared" si="13"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC46080-9CAB-4E93-A87F-CAF609E22C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EC5376-BEFE-433D-BC6A-96737E703EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57405" yWindow="1815" windowWidth="26355" windowHeight="18555" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -466,8 +466,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -507,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -517,16 +525,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,52 +1009,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="9"/>
+      <c r="H1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="9"/>
+      <c r="N1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="8" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2699,7 +2710,7 @@
       <c r="B48" s="1">
         <v>1522537</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="5">
         <v>78061</v>
       </c>
       <c r="D48" s="1">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EC5376-BEFE-433D-BC6A-96737E703EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89681E49-71B4-46DD-8075-7F85EEF8D6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
   </bookViews>
@@ -255,9 +255,6 @@
     <t xml:space="preserve">Дагестанская обл   </t>
   </si>
   <si>
-    <t xml:space="preserve">Елизаветпольская губ </t>
-  </si>
-  <si>
     <t>Карсская обл</t>
   </si>
   <si>
@@ -457,6 +454,9 @@
   </si>
   <si>
     <t>Таблица из ежегодника УГВИ стр. 3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Елисаветпольская губ </t>
   </si>
 </sst>
 </file>
@@ -875,95 +875,95 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
         <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -976,12 +976,12 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1029,35 +1029,35 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="M1" s="9"/>
       <c r="N1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1">
         <f>932539-B5</f>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1">
         <v>360000</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="1">
         <v>18628653</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="1">
         <v>716164</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="1">
         <v>10618585</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B70" s="1">
         <v>61961869</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="B75" s="1">
         <v>753395</v>
@@ -3784,29 +3784,29 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B76" s="1">
         <v>237114</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" s="1">
         <v>1286622</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1">
         <v>955000</v>
@@ -3857,7 +3857,7 @@
         <v>25.3</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K78" s="2">
         <f t="shared" si="4"/>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="1">
         <v>667511</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="1">
         <v>699875</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B81" s="1">
         <v>819264</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B82" s="1">
         <v>677491</v>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" s="1">
         <v>7438558</v>
@@ -4079,29 +4079,29 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" s="1">
         <v>63221</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="1">
         <v>458572</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" s="1">
         <v>545338</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="1">
         <v>421187</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B88" s="1">
         <v>102786</v>
@@ -4221,10 +4221,10 @@
         <v>1431</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K88" s="2">
         <f t="shared" si="4"/>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89" s="1">
         <v>1375455</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B90" s="1">
         <v>1256792</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B91" s="1">
         <v>255671</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B92" s="1">
         <v>14645</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B93" s="1">
         <v>4493667</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B94" s="1">
         <v>480874</v>
@@ -4479,51 +4479,51 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B95" s="1">
         <v>695922</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B96" s="1">
         <v>680135</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B97" s="1">
         <v>576578</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" s="1">
         <v>671878</v>
@@ -4571,10 +4571,10 @@
         <v>2566</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K98" s="2">
         <f t="shared" si="4"/>
@@ -4589,29 +4589,29 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B99" s="1">
         <v>1015760</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B100" s="1">
         <v>343485</v>
@@ -4623,10 +4623,10 @@
         <v>820</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K100" s="2">
         <f t="shared" si="4"/>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B101" s="1">
         <v>547162</v>
@@ -4653,10 +4653,10 @@
         <v>3053</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K101" s="2">
         <f t="shared" si="4"/>
@@ -4671,29 +4671,29 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B102" s="1">
         <v>716133</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B103" s="1">
         <v>5727927</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B104" s="1">
         <v>110482622</v>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89681E49-71B4-46DD-8075-7F85EEF8D6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687F3C3F-E25D-4A1A-A227-9921217D11CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
   </bookViews>
@@ -483,7 +483,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +502,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -515,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -536,6 +542,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1504,61 +1513,63 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
+      <c r="A16" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="11">
         <v>18628653</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="11">
         <v>858012</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="11">
         <v>527921</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="12">
         <v>46.9</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="12">
         <v>28.8</v>
       </c>
-      <c r="H16" s="1">
+      <c r="G16" s="10"/>
+      <c r="H16" s="11">
         <f>SUM(B3:B15)</f>
         <v>18628653</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="11">
         <f>SUM(C3:C15)</f>
         <v>858012</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="11">
         <f>SUM(D3:D15)</f>
         <v>527921</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="12">
         <f t="shared" si="0"/>
         <v>46.058724696842013</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="12">
         <f t="shared" si="1"/>
         <v>28.339193392028935</v>
       </c>
-      <c r="N16" s="1">
+      <c r="M16" s="10"/>
+      <c r="N16" s="11">
         <f>B16-H16</f>
         <v>0</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="11">
         <f>C16-I16</f>
         <v>0</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="11">
         <f>D16-J16</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="12">
         <f t="shared" si="2"/>
         <v>0.84127530315798538</v>
       </c>
-      <c r="R16" s="2">
+      <c r="R16" s="12">
         <f t="shared" si="3"/>
         <v>0.46080660797106532</v>
       </c>
@@ -2068,61 +2079,63 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+      <c r="A31" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="11">
         <v>10618585</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="11">
         <v>396239</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="11">
         <v>247395</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="12">
         <v>37.299999999999997</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="12">
         <v>23.3</v>
       </c>
-      <c r="H31" s="1">
+      <c r="G31" s="10"/>
+      <c r="H31" s="11">
         <f>SUM(B17:B30)</f>
         <v>10618585</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="11">
         <f>SUM(C17:C30)</f>
         <v>396239</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="11">
         <f>SUM(D17:D30)</f>
         <v>247395</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="12">
         <f t="shared" si="0"/>
         <v>37.315612202567479</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="12">
         <f t="shared" si="1"/>
         <v>23.298301986564123</v>
       </c>
-      <c r="N31" s="1">
+      <c r="M31" s="10"/>
+      <c r="N31" s="11">
         <f>B31-H31</f>
         <v>0</v>
       </c>
-      <c r="O31" s="1">
+      <c r="O31" s="11">
         <f>C31-I31</f>
         <v>0</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="11">
         <f>D31-J31</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="12">
         <f t="shared" si="2"/>
         <v>-1.5612202567481859E-2</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="12">
         <f t="shared" si="3"/>
         <v>1.698013435877499E-3</v>
       </c>
@@ -3496,61 +3509,63 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
+      <c r="A70" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="11">
         <v>61961869</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="11">
         <v>3034463</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="11">
         <v>2102507</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="12">
         <v>48.9</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="12">
         <v>33.9</v>
       </c>
-      <c r="H70" s="1">
+      <c r="G70" s="10"/>
+      <c r="H70" s="11">
         <f>SUM(B32:B69)</f>
         <v>61961869</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70" s="11">
         <f>SUM(C32:C69)</f>
         <v>3033663</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="11">
         <f>SUM(D32:D69)</f>
         <v>2102507</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="12">
         <f t="shared" si="4"/>
         <v>48.973070841358897</v>
       </c>
-      <c r="L70" s="2">
+      <c r="L70" s="12">
         <f t="shared" si="5"/>
         <v>33.932272120455245</v>
       </c>
-      <c r="N70" s="1">
+      <c r="M70" s="10"/>
+      <c r="N70" s="11">
         <f t="shared" ref="N70:P72" si="8">B70-H70</f>
         <v>0</v>
       </c>
-      <c r="O70" s="1">
+      <c r="O70" s="11">
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="P70" s="1">
+      <c r="P70" s="11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="12">
         <f t="shared" si="6"/>
         <v>-7.307084135889852E-2</v>
       </c>
-      <c r="R70" s="2">
+      <c r="R70" s="12">
         <f t="shared" si="7"/>
         <v>-3.2272120455246522E-2</v>
       </c>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687F3C3F-E25D-4A1A-A227-9921217D11CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E8FBA-EA2E-4429-B9E3-9F00D7FE39A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{588750BA-8C8C-462C-8265-CC5768323231}"/>
   </bookViews>
@@ -321,9 +321,6 @@
     <t>Тургайская</t>
   </si>
   <si>
-    <t>У ральская</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ферганская </t>
   </si>
   <si>
@@ -457,6 +454,9 @@
   </si>
   <si>
     <t xml:space="preserve">Елисаветпольская губ </t>
+  </si>
+  <si>
+    <t>Уральская</t>
   </si>
 </sst>
 </file>
@@ -884,95 +884,95 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" t="s">
         <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="E22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -985,12 +985,12 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1038,35 +1038,35 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="M1" s="9"/>
       <c r="N1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -1107,7 +1107,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="1">
         <f>932539-B5</f>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="1">
         <v>360000</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="11">
         <v>18628653</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B25" s="1">
         <v>716164</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="11">
         <v>10618585</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B70" s="11">
         <v>61961869</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B75" s="1">
         <v>753395</v>
@@ -3805,16 +3805,16 @@
         <v>237114</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
@@ -3872,7 +3872,7 @@
         <v>25.3</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K78" s="2">
         <f t="shared" si="4"/>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B83" s="1">
         <v>7438558</v>
@@ -4100,16 +4100,16 @@
         <v>63221</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
@@ -4236,10 +4236,10 @@
         <v>1431</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K88" s="2">
         <f t="shared" si="4"/>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B93" s="1">
         <v>4493667</v>
@@ -4500,16 +4500,16 @@
         <v>695922</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
@@ -4522,16 +4522,16 @@
         <v>680135</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B98" s="1">
         <v>671878</v>
@@ -4586,10 +4586,10 @@
         <v>2566</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K98" s="2">
         <f t="shared" si="4"/>
@@ -4610,16 +4610,16 @@
         <v>1015760</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
@@ -4638,10 +4638,10 @@
         <v>820</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K100" s="2">
         <f t="shared" si="4"/>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="B101" s="1">
         <v>547162</v>
@@ -4668,10 +4668,10 @@
         <v>3053</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K101" s="2">
         <f t="shared" si="4"/>
@@ -4686,29 +4686,29 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B102" s="1">
         <v>716133</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B103" s="1">
         <v>5727927</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B104" s="1">
         <v>110482622</v>
